--- a/addresses/mock_google_data/geocoding_cache.xlsx
+++ b/addresses/mock_google_data/geocoding_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,10 +474,8 @@
           <t>שערי תשובה</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="D2" t="n">
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>31.927077</v>
@@ -510,10 +508,8 @@
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="D3" t="n">
+        <v>43</v>
       </c>
       <c r="E3" t="n">
         <v>31.9396766</v>
@@ -546,10 +542,8 @@
           <t>רבי עקיבא</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="D4" t="n">
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>31.9406088</v>
@@ -582,10 +576,8 @@
           <t>נתיבות שלום</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="D5" t="n">
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>31.92844</v>
@@ -618,10 +610,8 @@
           <t>קצות החושן</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D6" t="n">
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>31.9279674</v>
@@ -654,10 +644,8 @@
           <t>רשבי</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D7" t="n">
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>31.9377883</v>
@@ -690,10 +678,8 @@
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="D8" t="n">
+        <v>25</v>
       </c>
       <c r="E8" t="n">
         <v>31.93938</v>
@@ -726,10 +712,8 @@
           <t>רבי שמעון בר יוחאי</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D9" t="n">
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -758,10 +742,8 @@
           <t>רשבי</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="D10" t="n">
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>31.9374409</v>
@@ -794,10 +776,8 @@
           <t>שדרות הרב מפונוביז</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D11" t="n">
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -826,10 +806,8 @@
           <t>הריטבא</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D12" t="n">
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>31.9273875</v>
@@ -862,10 +840,8 @@
           <t>שד הרב מפוניבז</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D13" t="n">
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -894,10 +870,8 @@
           <t>חזון איש</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="D14" t="n">
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>31.9222529</v>
@@ -930,10 +904,8 @@
           <t>רשבי</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="D15" t="n">
+        <v>18</v>
       </c>
       <c r="E15" t="n">
         <v>31.9372758</v>
@@ -966,10 +938,8 @@
           <t>רבי עקיבא</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="D16" t="n">
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>31.94064719999999</v>
@@ -1002,10 +972,8 @@
           <t>חזון איש</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D17" t="n">
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>31.9222529</v>
@@ -1038,10 +1006,8 @@
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="D18" t="n">
+        <v>21</v>
       </c>
       <c r="E18" t="n">
         <v>31.9395316</v>
@@ -1074,10 +1040,8 @@
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="D19" t="n">
+        <v>26</v>
       </c>
       <c r="E19" t="n">
         <v>31.938572</v>
@@ -1110,10 +1074,8 @@
           <t>רבי יהודה הנשיא</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="D20" t="n">
+        <v>41</v>
       </c>
       <c r="E20" t="n">
         <v>31.9396857</v>
@@ -1146,10 +1108,8 @@
           <t>חתם סופר</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D21" t="n">
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1178,10 +1138,8 @@
           <t>רשבי</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="D22" t="n">
+        <v>37</v>
       </c>
       <c r="E22" t="n">
         <v>31.9373403</v>
@@ -1214,10 +1172,8 @@
           <t>שדי חמד</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="D23" t="n">
+        <v>28</v>
       </c>
       <c r="E23" t="n">
         <v>31.9328825</v>
@@ -1250,10 +1206,8 @@
           <t>אור החיים</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="D24" t="n">
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>31.93264</v>
@@ -1286,10 +1240,8 @@
           <t>חזון דוד</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="D25" t="n">
+        <v>27</v>
       </c>
       <c r="E25" t="n">
         <v>31.9243742</v>
@@ -1322,10 +1274,8 @@
           <t>חזון דוד</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="D26" t="n">
+        <v>17</v>
       </c>
       <c r="E26" t="n">
         <v>31.9257054</v>
@@ -1358,10 +1308,8 @@
           <t>חזון איש</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="D27" t="n">
+        <v>15</v>
       </c>
       <c r="E27" t="n">
         <v>31.9221798</v>
@@ -1394,10 +1342,8 @@
           <t>נתיבות המשפט</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="D28" t="n">
+        <v>93</v>
       </c>
       <c r="E28" t="n">
         <v>31.9257393</v>
@@ -1430,10 +1376,8 @@
           <t>מסילת יוסף</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D29" t="n">
+        <v>50</v>
       </c>
       <c r="E29" t="n">
         <v>31.9272384</v>
@@ -1466,10 +1410,8 @@
           <t>רבי שמעון בר יוחאי</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="D30" t="n">
+        <v>14</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1498,10 +1440,8 @@
           <t>נתיבות המשפט</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D31" t="n">
+        <v>85</v>
       </c>
       <c r="E31" t="n">
         <v>31.9245194</v>
@@ -1534,10 +1474,8 @@
           <t>משך חכמה</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="D32" t="n">
+        <v>80</v>
       </c>
       <c r="E32" t="n">
         <v>31.932933</v>
@@ -1570,10 +1508,8 @@
           <t>משך חכמה</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="D33" t="n">
+        <v>60</v>
       </c>
       <c r="E33" t="n">
         <v>31.9337067</v>
@@ -1606,10 +1542,8 @@
           <t>שערי תשובה</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="D34" t="n">
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>31.927077</v>
@@ -1642,10 +1576,8 @@
           <t>שאגת אריה</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D35" t="n">
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>31.9290753</v>
@@ -1678,10 +1610,8 @@
           <t>רמבם</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="D36" t="n">
+        <v>18</v>
       </c>
       <c r="E36" t="n">
         <v>31.9293284</v>
@@ -1714,10 +1644,8 @@
           <t>נתיבות המשפט</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="D37" t="n">
+        <v>71</v>
       </c>
       <c r="E37" t="n">
         <v>31.9259043</v>
@@ -1750,10 +1678,8 @@
           <t>מסילת יוסף</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="D38" t="n">
+        <v>19</v>
       </c>
       <c r="E38" t="n">
         <v>31.926859</v>
@@ -1786,10 +1712,8 @@
           <t>אבני נזר</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="D39" t="n">
+        <v>21</v>
       </c>
       <c r="E39" t="n">
         <v>31.9346348</v>
@@ -1822,10 +1746,8 @@
           <t>מסילת ישרים</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D40" t="n">
+        <v>40</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1841,1051 +1763,985 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>רחוב סביון 38, רכסים</t>
+          <t>אבני נזר 12, מודיעין עילית</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>רחוב סביון</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>אבני נזר</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>32.755329</v>
+        <v>31.934894</v>
       </c>
       <c r="F41" t="n">
-        <v>35.1036374</v>
+        <v>35.043743</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>google precise match: סביון 38, רכסים, ישראל</t>
+          <t>google precise match: אבני נזר 12, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>רחוב סביון 38, רכסים</t>
+          <t>מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>רחוב סביון</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>מסילת יוסף</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>32.755329</v>
+        <v>31.9312516</v>
       </c>
       <c r="F42" t="n">
-        <v>35.1036374</v>
+        <v>35.045036</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>google precise match: סביון 38, רכסים, ישראל</t>
+          <t>google precise match: מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>הכלניות 47, רכסים</t>
+          <t>מרומי שדה 3, מודיעין עילית</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+          <t>מרומי שדה</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>32.7535253</v>
+        <v>31.9286714</v>
       </c>
       <c r="F43" t="n">
-        <v>35.10205910000001</v>
+        <v>35.0440405</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 47, רכסים, ישראל</t>
+          <t>google precise match: מרומי שדה 3, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>הכלניות 37, רכסים</t>
+          <t>רשבם 8, מודיעין עילית</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>32.7535535</v>
-      </c>
-      <c r="F44" t="n">
-        <v>35.1006119</v>
-      </c>
+          <t>רשבם</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 37, רכסים, ישראל</t>
+          <t>google could not accurately find this address</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>הכלניות 37, רכסים</t>
+          <t>שדי חמד 15, מודיעין עילית</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>שדי חמד</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>15</v>
       </c>
       <c r="E45" t="n">
-        <v>32.7535535</v>
+        <v>31.93349499999999</v>
       </c>
       <c r="F45" t="n">
-        <v>35.1006119</v>
+        <v>35.042305</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 37, רכסים, ישראל</t>
+          <t>google precise match: רח' שדי חמד 15, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>כלניות 17, רכסים</t>
+          <t>רמבם 18, מודיעין עילית</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>כלניות</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>רמבם</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>32.7537489</v>
+        <v>31.9293284</v>
       </c>
       <c r="F46" t="n">
-        <v>35.0992594</v>
+        <v>35.0465972</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 17, רכסים, ישראל</t>
+          <t>google precise match: רמב"ם 18, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>הכלניות 1, רכסים</t>
+          <t>רבי יהודה הנשיא 37, מודיעין עילית</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>רבי יהודה הנשיא</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>37</v>
       </c>
       <c r="E47" t="n">
-        <v>32.7541406</v>
+        <v>31.9390725</v>
       </c>
       <c r="F47" t="n">
-        <v>35.0975422</v>
+        <v>35.0452352</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 1, רכסים, ישראל</t>
+          <t>google precise match: רבי יהודה הנשיא 37, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>הורדים 4, רכסים</t>
+          <t>מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>הורדים</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>מסילת יוסף</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>32.755216</v>
+        <v>31.9312516</v>
       </c>
       <c r="F48" t="n">
-        <v>35.0965091</v>
+        <v>35.045036</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>google precise match: הורדים 4, רכסים, 20496, ישראל</t>
+          <t>google precise match: מסילת יוסף 14, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ורדים 5, רכסים</t>
+          <t>חזון דוד 25, מודיעין עילית</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ורדים</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>חזון דוד</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>25</v>
       </c>
       <c r="E49" t="n">
-        <v>32.7558831</v>
+        <v>31.924268</v>
       </c>
       <c r="F49" t="n">
-        <v>35.0962669</v>
+        <v>35.043069</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>google precise match: הורדים 5, רכסים, ישראל</t>
+          <t>google precise match: חזון דוד 25, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>הנרקיסים 28, רכסים</t>
+          <t>חזון איש 21, מודיעין עילית</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>הנרקיסים</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>חזון איש</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>21</v>
       </c>
       <c r="E50" t="n">
-        <v>32.756526</v>
+        <v>31.9219767</v>
       </c>
       <c r="F50" t="n">
-        <v>35.0985092</v>
+        <v>35.0528416</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>google precise match: הנרקיסים 28, רכסים, ישראל</t>
+          <t>google precise match: חזון אי"ש 21, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>הנרקיסים 24, רכסים</t>
+          <t>חזון איש 21, מודיעין עילית</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>הנרקיסים</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>חזון איש</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>21</v>
       </c>
       <c r="E51" t="n">
-        <v>32.7564592</v>
+        <v>31.9219767</v>
       </c>
       <c r="F51" t="n">
-        <v>35.0993751</v>
+        <v>35.0528416</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>google precise match: הנרקיסים 24, רכסים, ישראל</t>
+          <t>google precise match: חזון אי"ש 21, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>הכלניות 38, רכסים</t>
+          <t>רבי יהודה הנשיא 20, מודיעין עילית</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>רבי יהודה הנשיא</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>32.7536982</v>
+        <v>31.9385733</v>
       </c>
       <c r="F52" t="n">
-        <v>35.1009379</v>
+        <v>35.0430685</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 38, רכסים, ישראל</t>
+          <t>google precise match: רבי יהודה הנשיא 20, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>הכלניות 36, רכסים</t>
+          <t>חפץ חיים 21, מודיעין עילית</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>חפץ חיים</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>21</v>
       </c>
       <c r="E53" t="n">
-        <v>32.7538063</v>
+        <v>31.9301503</v>
       </c>
       <c r="F53" t="n">
-        <v>35.1005274</v>
+        <v>35.042627</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 36, רכסים, ישראל</t>
+          <t>google precise match: רחוב חפץ חיים 21, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>הכלניות 32, רכסים</t>
+          <t>רשבי 32, מודיעין עילית</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>הכלניות</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>רשבי</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>32</v>
       </c>
       <c r="E54" t="n">
-        <v>32.753939</v>
+        <v>31.9369865</v>
       </c>
       <c r="F54" t="n">
-        <v>35.09969299999999</v>
+        <v>35.0450276</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>google precise match: הכלניות 32, רכסים, ישראל</t>
+          <t>google precise match: רבי שמעון בר יוחאי 32, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>רחוב הזית 13, רכסים</t>
+          <t>נתיבות המשפט 107, מודיעין עילית</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>רחוב הזית</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>107</v>
       </c>
       <c r="E55" t="n">
-        <v>32.7555378</v>
+        <v>31.927568</v>
       </c>
       <c r="F55" t="n">
-        <v>35.101955</v>
+        <v>35.038982</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>google precise match: זית 13, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 107, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>רחוב הזית 13, רכסים</t>
+          <t>נתיבות המשפט 99, מודיעין עילית</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>רחוב הזית</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>99</v>
       </c>
       <c r="E56" t="n">
-        <v>32.7555378</v>
+        <v>31.9268206</v>
       </c>
       <c r="F56" t="n">
-        <v>35.101955</v>
+        <v>35.0405249</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>google precise match: זית 13, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 99, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>הדקל 30, רכסים</t>
+          <t>חזון איש 23, מודיעין עילית</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>הדקל</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>חזון איש</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>23</v>
       </c>
       <c r="E57" t="n">
-        <v>32.7552473</v>
+        <v>31.92194</v>
       </c>
       <c r="F57" t="n">
-        <v>35.1072159</v>
+        <v>35.0532167</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>google precise match: דקל 30, רכסים, ישראל</t>
+          <t>google precise match: חזון אי"ש 23, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>הדס 4, רכסים</t>
+          <t>נתיבות המשפט 59, מודיעין עילית</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>הדס</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>59</v>
       </c>
       <c r="E58" t="n">
-        <v>32.7551946</v>
+        <v>31.9278568</v>
       </c>
       <c r="F58" t="n">
-        <v>35.1066628</v>
+        <v>35.0452741</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>google precise match: הדס 4, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 59, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>הדס 6, רכסים</t>
+          <t>רשבי 38, מודיעין עילית</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>הדס</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>רשבי</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>38</v>
       </c>
       <c r="E59" t="n">
-        <v>32.755124</v>
+        <v>31.9377739</v>
       </c>
       <c r="F59" t="n">
-        <v>35.106438</v>
+        <v>35.0462969</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>google precise match: הדס 6, רכסים, 20496, ישראל</t>
+          <t>google precise match: רבי שמעון בר יוחאי 38, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>אשל 5, רכסים</t>
+          <t>מסילת יוסף 44, מודיעין עילית</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>אשל</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>מסילת יוסף</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>44</v>
       </c>
       <c r="E60" t="n">
-        <v>32.7537724</v>
+        <v>31.9276112</v>
       </c>
       <c r="F60" t="n">
-        <v>35.107609</v>
+        <v>35.042819</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>google precise match: אשל 5, רכסים, ישראל</t>
+          <t>google precise match: מסילת יוסף 44, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>דקל 2, רכסים</t>
+          <t>נתיבות המשפט 85, מודיעין עילית</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>דקל</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>85</v>
       </c>
       <c r="E61" t="n">
-        <v>32.7531176</v>
+        <v>31.9245194</v>
       </c>
       <c r="F61" t="n">
-        <v>35.10734310000001</v>
+        <v>35.0419395</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>google precise match: דקל 2, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 85, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>השקד 13, רכסים</t>
+          <t>רמבם 32, מודיעין עילית</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>השקד</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>32.752189</v>
-      </c>
-      <c r="F62" t="n">
-        <v>35.103784</v>
-      </c>
+          <t>רמבם</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>32</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>google precise match: השקד 13, רכסים, ישראל</t>
+          <t>google found a precise address, but not in the requested city</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>השקד 14, רכסים</t>
+          <t>חזון איש 7, מודיעין עילית</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>השקד</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>חזון איש</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>32.750799</v>
+        <v>31.9226253</v>
       </c>
       <c r="F63" t="n">
-        <v>35.102316</v>
+        <v>35.049516</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>google precise match: השקד 14, רכסים, ישראל</t>
+          <t>google precise match: חזון אי"ש 7, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>השקד 40, רכסים</t>
+          <t>קצות החושן 17, מודיעין עילית</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>השקד</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>קצות החושן</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>32.74899</v>
+        <v>31.9283181</v>
       </c>
       <c r="F64" t="n">
-        <v>35.103904</v>
+        <v>35.0395641</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>google precise match: השקד 40, רכסים, 2049600, ישראל</t>
+          <t>google precise match: רחוב קצות החושן 17, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>השקד 50, רכסים</t>
+          <t>נתיבות המשפט 3, מודיעין עילית</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>השקד</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>32.748611</v>
+        <v>31.9336533</v>
       </c>
       <c r="F65" t="n">
-        <v>35.104848</v>
+        <v>35.04736200000001</v>
       </c>
       <c r="G65" t="b">
         <v>1</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>google precise match: השקד 50, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 3, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>השקד 59, רכסים</t>
+          <t>רשבי 22, מודיעין עילית</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>השקד</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+          <t>רשבי</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>22</v>
       </c>
       <c r="E66" t="n">
-        <v>32.7484557</v>
+        <v>31.9370797</v>
       </c>
       <c r="F66" t="n">
-        <v>35.1065067</v>
+        <v>35.0430294</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>google precise match: השקד 59, רכסים, ישראל</t>
+          <t>google precise match: רבי שמעון בר יוחאי 22, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>מעלה החזון איש 13, רכסים</t>
+          <t>אשר לשלמה 1, מודיעין עילית</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>מעלה החזון איש</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>אשר לשלמה</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>32.751018</v>
+        <v>31.9232333</v>
       </c>
       <c r="F67" t="n">
-        <v>35.104936</v>
+        <v>35.0458679</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>google precise match: חזון איש 13, רכסים, ישראל</t>
+          <t>google precise match: אשר לשלמה 1, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>חזון איש 8, רכסים</t>
+          <t>רשבי 22, מודיעין עילית</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>חזון איש</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>רשבי</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>22</v>
       </c>
       <c r="E68" t="n">
-        <v>32.751478</v>
+        <v>31.9370797</v>
       </c>
       <c r="F68" t="n">
-        <v>35.104805</v>
+        <v>35.0430294</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>google precise match: חזון איש 8, רכסים, ישראל</t>
+          <t>google precise match: רבי שמעון בר יוחאי 22, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>רימונים 15, רכסים</t>
+          <t>נתיבות המשפט 3, מודיעין עילית</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>רימונים</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>נתיבות המשפט</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>32.7502502</v>
+        <v>31.9336533</v>
       </c>
       <c r="F69" t="n">
-        <v>35.0984128</v>
+        <v>35.04736200000001</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>google precise match: הרימונים 15, רכסים, ישראל</t>
+          <t>google precise match: נתיבות המשפט 3, מודיעין עילית</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>הרימונים 16, רכסים</t>
+          <t>רחוב סביון 38, רכסים</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2895,33 +2751,31 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>הרימונים</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>רחוב סביון</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>38</v>
       </c>
       <c r="E70" t="n">
-        <v>32.7499409</v>
+        <v>32.755329</v>
       </c>
       <c r="F70" t="n">
-        <v>35.0985743</v>
+        <v>35.1036374</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>google precise match: הרימונים 16, רכסים, ישראל</t>
+          <t>google precise match: סביון 38, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>הרב קוק 26, רכסים</t>
+          <t>רחוב סביון 38, רכסים</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2931,33 +2785,31 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>הרב קוק</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+          <t>רחוב סביון</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>38</v>
       </c>
       <c r="E71" t="n">
-        <v>32.7472521</v>
+        <v>32.755329</v>
       </c>
       <c r="F71" t="n">
-        <v>35.1022188</v>
+        <v>35.1036374</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>google precise match: הרב קוק 26, רכסים, ישראל</t>
+          <t>google precise match: סביון 38, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>הרב קוק 20, רכסים</t>
+          <t>הכלניות 47, רכסים</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2967,33 +2819,31 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>הרב קוק</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>47</v>
       </c>
       <c r="E72" t="n">
-        <v>32.7469827</v>
+        <v>32.7535253</v>
       </c>
       <c r="F72" t="n">
-        <v>35.1014102</v>
+        <v>35.10205910000001</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>google precise match: הרב קוק 20, רכסים, ישראל</t>
+          <t>google precise match: הכלניות 47, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>הרב קוק 31, רכסים</t>
+          <t>הכלניות 37, רכסים</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3003,33 +2853,31 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>הרב קוק</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>37</v>
       </c>
       <c r="E73" t="n">
-        <v>32.746403</v>
+        <v>32.7535535</v>
       </c>
       <c r="F73" t="n">
-        <v>35.101053</v>
+        <v>35.1006119</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>google precise match: הרב קוק 31, רכסים, ישראל</t>
+          <t>google precise match: הכלניות 37, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>הרב קוק 14, רכסים</t>
+          <t>הכלניות 37, רכסים</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3039,33 +2887,31 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>הרב קוק</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>37</v>
       </c>
       <c r="E74" t="n">
-        <v>32.7466012</v>
+        <v>32.7535535</v>
       </c>
       <c r="F74" t="n">
-        <v>35.1003358</v>
+        <v>35.1006119</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>google precise match: הרב קוק 14, רכסים, ישראל</t>
+          <t>google precise match: הכלניות 37, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>הרב קוק 12, רכסים</t>
+          <t>כלניות 17, רכסים</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3075,1069 +2921,1017 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>הרב קוק</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>כלניות</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>17</v>
       </c>
       <c r="E75" t="n">
-        <v>32.7465011</v>
+        <v>32.7537489</v>
       </c>
       <c r="F75" t="n">
-        <v>35.1002575</v>
+        <v>35.0992594</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>google precise match: הרב קוק 12, רכסים, ישראל</t>
+          <t>google precise match: הכלניות 17, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 46, לוד</t>
+          <t>הכלניות 1, רכסים</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>31.9417</v>
+        <v>32.7541406</v>
       </c>
       <c r="F76" t="n">
-        <v>34.901168</v>
+        <v>35.0975422</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>google precise match: יחד שבטי ישראל 46, לוד, ישראל</t>
+          <t>google precise match: הכלניות 1, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>משה רבינו 6, לוד</t>
+          <t>הורדים 4, רכסים</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>משה רבינו</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>הורדים</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>31.9377122</v>
+        <v>32.755216</v>
       </c>
       <c r="F77" t="n">
-        <v>34.8994915</v>
+        <v>35.0965091</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>google precise match: משה רבנו 6, לוד, ישראל</t>
+          <t>google precise match: הורדים 4, רכסים, 20496, ישראל</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>השייטת 3, לוד</t>
+          <t>ורדים 5, רכסים</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>השייטת</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>ורדים</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>31.9423725</v>
+        <v>32.7558831</v>
       </c>
       <c r="F78" t="n">
-        <v>34.8787121</v>
+        <v>35.0962669</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>google precise match: שייטת 3, לוד, ישראל</t>
+          <t>google precise match: הורדים 5, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 8, לוד</t>
+          <t>הנרקיסים 28, רכסים</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+          <t>הנרקיסים</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>28</v>
+      </c>
+      <c r="E79" t="n">
+        <v>32.756526</v>
+      </c>
+      <c r="F79" t="n">
+        <v>35.0985092</v>
+      </c>
       <c r="G79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>google could not accurately find this address</t>
+          <t>google precise match: הנרקיסים 28, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>צמח צדק 5, לוד</t>
+          <t>הנרקיסים 24, רכסים</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>הנרקיסים</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>24</v>
       </c>
       <c r="E80" t="n">
-        <v>31.942521</v>
+        <v>32.7564592</v>
       </c>
       <c r="F80" t="n">
-        <v>34.8761029</v>
+        <v>35.0993751</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 5, לוד, ישראל</t>
+          <t>google precise match: הנרקיסים 24, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>צמח צדק 7, לוד</t>
+          <t>הכלניות 38, רכסים</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>38</v>
       </c>
       <c r="E81" t="n">
-        <v>31.9421204</v>
+        <v>32.7536982</v>
       </c>
       <c r="F81" t="n">
-        <v>34.8759688</v>
+        <v>35.1009379</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 7, לוד, 7132127, ישראל</t>
+          <t>google precise match: הכלניות 38, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>שבט יהודה 7, לוד</t>
+          <t>הכלניות 36, רכסים</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>שבט יהודה</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>36</v>
       </c>
       <c r="E82" t="n">
-        <v>31.9364842</v>
+        <v>32.7538063</v>
       </c>
       <c r="F82" t="n">
-        <v>34.8981627</v>
+        <v>35.1005274</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>google precise match: שבט יהודה 7, לוד, ישראל</t>
+          <t>google precise match: הכלניות 36, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>צמח צדק 7, לוד</t>
+          <t>הכלניות 32, רכסים</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>הכלניות</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>32</v>
       </c>
       <c r="E83" t="n">
-        <v>31.9421204</v>
+        <v>32.753939</v>
       </c>
       <c r="F83" t="n">
-        <v>34.8759688</v>
+        <v>35.09969299999999</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 7, לוד, 7132127, ישראל</t>
+          <t>google precise match: הכלניות 32, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 12, לוד</t>
+          <t>רחוב הזית 13, רכסים</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>רחוב הזית</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13</v>
       </c>
       <c r="E84" t="n">
-        <v>31.938619</v>
+        <v>32.7555378</v>
       </c>
       <c r="F84" t="n">
-        <v>34.898745</v>
+        <v>35.101955</v>
       </c>
       <c r="G84" t="b">
         <v>1</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>google precise match: יחד שבטי ישראל 12, לוד, ישראל</t>
+          <t>google precise match: זית 13, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>שבט אשר 7, לוד</t>
+          <t>רחוב הזית 13, רכסים</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>שבט אשר</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>רחוב הזית</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13</v>
       </c>
       <c r="E85" t="n">
-        <v>31.93523</v>
+        <v>32.7555378</v>
       </c>
       <c r="F85" t="n">
-        <v>34.899036</v>
+        <v>35.101955</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>google precise match: שבט אשר 7, לוד, ישראל</t>
+          <t>google precise match: זית 13, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>שבט יהודה 3, לוד</t>
+          <t>הדקל 30, רכסים</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>שבט יהודה</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>הדקל</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>30</v>
       </c>
       <c r="E86" t="n">
-        <v>31.9361173</v>
+        <v>32.7552473</v>
       </c>
       <c r="F86" t="n">
-        <v>34.8991023</v>
+        <v>35.1072159</v>
       </c>
       <c r="G86" t="b">
         <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>google precise match: שבט יהודה 3, לוד, ישראל</t>
+          <t>google precise match: דקל 30, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>צמח צדק 5, לוד</t>
+          <t>הדס 4, רכסים</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>הדס</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>31.942521</v>
+        <v>32.7551946</v>
       </c>
       <c r="F87" t="n">
-        <v>34.8761029</v>
+        <v>35.1066628</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 5, לוד, ישראל</t>
+          <t>google precise match: הדס 4, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>אחיסמך רבקה אימנו 43, לוד</t>
+          <t>הדס 6, רכסים</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>אחיסמך רבקה אימנו</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t>הדס</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>31.941588</v>
+        <v>32.755124</v>
       </c>
       <c r="F88" t="n">
-        <v>34.898604</v>
+        <v>35.106438</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>google precise match: רבקה אימנו 43, לוד, ישראל</t>
+          <t>google precise match: הדס 6, רכסים, 20496, ישראל</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>שבט יהודה 8, לוד</t>
+          <t>אשל 5, רכסים</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>שבט יהודה</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>אשל</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>31.936617</v>
+        <v>32.7537724</v>
       </c>
       <c r="F89" t="n">
-        <v>34.8981782</v>
+        <v>35.107609</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>google precise match: שבט יהודה 8, לוד, ישראל</t>
+          <t>google precise match: אשל 5, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>שבט זבולון 15, לוד</t>
+          <t>דקל 2, רכסים</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>שבט זבולון</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>דקל</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>31.9407644</v>
+        <v>32.7531176</v>
       </c>
       <c r="F90" t="n">
-        <v>34.9026071</v>
+        <v>35.10734310000001</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>google precise match: שבט זבולון 15, לוד, ישראל</t>
+          <t>google precise match: דקל 2, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>שבט זבולון 11, לוד</t>
+          <t>השקד 13, רכסים</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>שבט זבולון</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>השקד</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>13</v>
       </c>
       <c r="E91" t="n">
-        <v>31.939077</v>
+        <v>32.752189</v>
       </c>
       <c r="F91" t="n">
-        <v>34.901074</v>
+        <v>35.103784</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>google precise match: שבט זבולון 11, לוד, ישראל</t>
+          <t>google precise match: השקד 13, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>יעקב אבינו 12, לוד</t>
+          <t>השקד 14, רכסים</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>יעקב אבינו</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>השקד</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>31.936225</v>
+        <v>32.750799</v>
       </c>
       <c r="F92" t="n">
-        <v>34.897088</v>
+        <v>35.102316</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>google precise match: יעקב אבינו 12, לוד, ישראל</t>
+          <t>google precise match: השקד 14, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>צמח צדק 9, לוד</t>
+          <t>השקד 40, רכסים</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>השקד</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>40</v>
       </c>
       <c r="E93" t="n">
-        <v>31.9419786</v>
+        <v>32.74899</v>
       </c>
       <c r="F93" t="n">
-        <v>34.8754465</v>
+        <v>35.103904</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 9, לוד, ישראל</t>
+          <t>google precise match: השקד 40, רכסים, 2049600, ישראל</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>שבט אשר 30, לוד</t>
+          <t>השקד 50, רכסים</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>שבט אשר</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>השקד</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>31.9346921</v>
+        <v>32.748611</v>
       </c>
       <c r="F94" t="n">
-        <v>34.8993058</v>
+        <v>35.104848</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>google precise match: שבט אשר 30, לוד, ישראל</t>
+          <t>google precise match: השקד 50, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>בעל התניא 9, לוד</t>
+          <t>השקד 59, רכסים</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>בעל התניא</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>השקד</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>59</v>
       </c>
       <c r="E95" t="n">
-        <v>31.9418437</v>
+        <v>32.7484557</v>
       </c>
       <c r="F95" t="n">
-        <v>34.8737541</v>
+        <v>35.1065067</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>google precise match: בעל התניא 9, לוד, 7132162, ישראל</t>
+          <t>google precise match: השקד 59, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>שבט יהודה 16, לוד</t>
+          <t>מעלה החזון איש 13, רכסים</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>שבט יהודה</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>מעלה החזון איש</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>13</v>
       </c>
       <c r="E96" t="n">
-        <v>31.9375477</v>
+        <v>32.751018</v>
       </c>
       <c r="F96" t="n">
-        <v>34.89564000000001</v>
+        <v>35.104936</v>
       </c>
       <c r="G96" t="b">
         <v>1</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>google precise match: שבט יהודה 16, לוד, ישראל</t>
+          <t>google precise match: חזון איש 13, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 1, לוד</t>
+          <t>חזון איש 8, רכסים</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>חזון איש</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>31.938619</v>
+        <v>32.751478</v>
       </c>
       <c r="F97" t="n">
-        <v>34.898745</v>
+        <v>35.104805</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>google precise match: יחד שבטי ישראל 1, לוד, ישראל</t>
+          <t>google precise match: חזון איש 8, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 21, לוד</t>
+          <t>רימונים 15, רכסים</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>רימונים</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>15</v>
       </c>
       <c r="E98" t="n">
-        <v>31.938619</v>
+        <v>32.7502502</v>
       </c>
       <c r="F98" t="n">
-        <v>34.898745</v>
+        <v>35.0984128</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>google precise match: יחד שבטי ישראל 21, לוד, ישראל</t>
+          <t>google precise match: הרימונים 15, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>שבט אפרים 32, לוד</t>
+          <t>הרימונים 16, רכסים</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>שבט אפרים</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>הרימונים</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>31.9397533</v>
+        <v>32.7499409</v>
       </c>
       <c r="F99" t="n">
-        <v>34.9003686</v>
+        <v>35.0985743</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>google precise match: שבט אפרים 32, לוד, ישראל</t>
+          <t>google precise match: הרימונים 16, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>שבטי ישראל 25, לוד</t>
+          <t>הרב קוק 26, רכסים</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+          <t>הרב קוק</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>26</v>
+      </c>
+      <c r="E100" t="n">
+        <v>32.7472521</v>
+      </c>
+      <c r="F100" t="n">
+        <v>35.1022188</v>
+      </c>
       <c r="G100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>google could not accurately find this address</t>
+          <t>google precise match: הרב קוק 26, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>שבט זבולון 20, לוד</t>
+          <t>הרב קוק 20, רכסים</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>שבט זבולון</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>הרב קוק</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>20</v>
       </c>
       <c r="E101" t="n">
-        <v>31.9409507</v>
+        <v>32.7469827</v>
       </c>
       <c r="F101" t="n">
-        <v>34.902678</v>
+        <v>35.1014102</v>
       </c>
       <c r="G101" t="b">
         <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>google precise match: שבט זבולון 20, לוד, ישראל</t>
+          <t>google precise match: הרב קוק 20, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>שבט אפרים 3, לוד</t>
+          <t>הרב קוק 31, רכסים</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>שבט אפרים</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>הרב קוק</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>31</v>
       </c>
       <c r="E102" t="n">
-        <v>31.939291</v>
+        <v>32.746403</v>
       </c>
       <c r="F102" t="n">
-        <v>34.900613</v>
+        <v>35.101053</v>
       </c>
       <c r="G102" t="b">
         <v>1</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>google precise match: שבט אפרים 3, לוד, ישראל</t>
+          <t>google precise match: הרב קוק 31, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>שבט אשר 21, לוד</t>
+          <t>הרב קוק 14, רכסים</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>שבט אשר</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>הרב קוק</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>31.9348377</v>
+        <v>32.7466012</v>
       </c>
       <c r="F103" t="n">
-        <v>34.8988273</v>
+        <v>35.1003358</v>
       </c>
       <c r="G103" t="b">
         <v>1</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>google precise match: שבט אשר 21, לוד, ישראל</t>
+          <t>google precise match: הרב קוק 14, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>הרב עובדיה יוסף 19, לוד</t>
+          <t>הרב קוק 12, רכסים</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>הרב עובדיה יוסף</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>הרב קוק</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12</v>
       </c>
       <c r="E104" t="n">
-        <v>31.9406476</v>
+        <v>32.7465011</v>
       </c>
       <c r="F104" t="n">
-        <v>34.9018068</v>
+        <v>35.1002575</v>
       </c>
       <c r="G104" t="b">
         <v>1</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>google precise match: הרב עובדיה יוסף 19, לוד, ישראל</t>
+          <t>google precise match: הרב קוק 12, רכסים, ישראל</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>משה רבינו 5, לוד</t>
+          <t>יחד שבטי ישראל 46, לוד</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4147,33 +3941,31 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>משה רבינו</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>46</v>
       </c>
       <c r="E105" t="n">
-        <v>31.9373491</v>
+        <v>31.9417</v>
       </c>
       <c r="F105" t="n">
-        <v>34.899169</v>
+        <v>34.901168</v>
       </c>
       <c r="G105" t="b">
         <v>1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>google precise match: משה רבנו 5, לוד, ישראל</t>
+          <t>google precise match: יחד שבטי ישראל 46, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל 7, לוד</t>
+          <t>משה רבינו 6, לוד</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4183,33 +3975,31 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>יחד שבטי ישראל</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>משה רבינו</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>6</v>
       </c>
       <c r="E106" t="n">
-        <v>31.938619</v>
+        <v>31.9377122</v>
       </c>
       <c r="F106" t="n">
-        <v>34.898745</v>
+        <v>34.8994915</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>google precise match: יחד שבטי ישראל 7, לוד, ישראל</t>
+          <t>google precise match: משה רבנו 6, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>שבט אפרים 10, לוד</t>
+          <t>השייטת 3, לוד</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4219,33 +4009,31 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>שבט אפרים</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>השייטת</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>31.939803</v>
+        <v>31.9423725</v>
       </c>
       <c r="F107" t="n">
-        <v>34.900226</v>
+        <v>34.8787121</v>
       </c>
       <c r="G107" t="b">
         <v>1</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>google precise match: שבט אפרים 10, לוד, ישראל</t>
+          <t>google precise match: שייטת 3, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>צמח צדק 4, לוד</t>
+          <t>יחד שבטי ישראל 8, לוד</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4255,33 +4043,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>צמח צדק</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>31.9431631</v>
-      </c>
-      <c r="F108" t="n">
-        <v>34.87565</v>
-      </c>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 4, לוד, 7132117, ישראל</t>
+          <t>google could not accurately find this address</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>צמח צדק 9, לוד</t>
+          <t>צמח צדק 5, לוד</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4294,30 +4076,28 @@
           <t>צמח צדק</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="D109" t="n">
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>31.9419786</v>
+        <v>31.942521</v>
       </c>
       <c r="F109" t="n">
-        <v>34.8754465</v>
+        <v>34.8761029</v>
       </c>
       <c r="G109" t="b">
         <v>1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>google precise match: צמח צדק 9, לוד, ישראל</t>
+          <t>google precise match: צמח צדק 5, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>משה רבנו 17, לוד</t>
+          <t>צמח צדק 7, לוד</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4327,33 +4107,31 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>משה רבנו</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7</v>
       </c>
       <c r="E110" t="n">
-        <v>31.9385218</v>
+        <v>31.9421204</v>
       </c>
       <c r="F110" t="n">
-        <v>34.8970749</v>
+        <v>34.8759688</v>
       </c>
       <c r="G110" t="b">
         <v>1</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>google precise match: משה רבנו 17, לוד, ישראל</t>
+          <t>google precise match: צמח צדק 7, לוד, 7132127, ישראל</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>שבט זבולון 21, לוד</t>
+          <t>שבט יהודה 7, לוד</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4363,33 +4141,31 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>שבט זבולון</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>שבט יהודה</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7</v>
       </c>
       <c r="E111" t="n">
-        <v>31.9411508</v>
+        <v>31.9364842</v>
       </c>
       <c r="F111" t="n">
-        <v>34.9025428</v>
+        <v>34.8981627</v>
       </c>
       <c r="G111" t="b">
         <v>1</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>google precise match: שבט זבולון 21, לוד, ישראל</t>
+          <t>google precise match: שבט יהודה 7, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>יצחק אבינו 8, לוד</t>
+          <t>צמח צדק 7, לוד</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4399,33 +4175,31 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>יצחק אבינו</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>7</v>
       </c>
       <c r="E112" t="n">
-        <v>31.93571</v>
+        <v>31.9421204</v>
       </c>
       <c r="F112" t="n">
-        <v>34.896836</v>
+        <v>34.8759688</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>google precise match: יעקב אבינו 8, לוד, ישראל</t>
+          <t>google precise match: צמח צדק 7, לוד, 7132127, ישראל</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>יעקב אבינו 7, לוד</t>
+          <t>יחד שבטי ישראל 12, לוד</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4435,52 +4209,1030 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>יעקב אבינו</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12</v>
+      </c>
+      <c r="E113" t="n">
+        <v>31.938619</v>
+      </c>
+      <c r="F113" t="n">
+        <v>34.898745</v>
+      </c>
       <c r="G113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>google could not accurately find this address</t>
+          <t>google precise match: יחד שבטי ישראל 12, לוד, ישראל</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>שבט אשר 7, לוד</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>שבט אשר</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="n">
+        <v>31.93523</v>
+      </c>
+      <c r="F114" t="n">
+        <v>34.899036</v>
+      </c>
+      <c r="G114" t="b">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אשר 7, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>שבט יהודה 3, לוד</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>שבט יהודה</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>31.9361173</v>
+      </c>
+      <c r="F115" t="n">
+        <v>34.8991023</v>
+      </c>
+      <c r="G115" t="b">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>google precise match: שבט יהודה 3, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>צמח צדק 5, לוד</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" t="n">
+        <v>31.942521</v>
+      </c>
+      <c r="F116" t="n">
+        <v>34.8761029</v>
+      </c>
+      <c r="G116" t="b">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>google precise match: צמח צדק 5, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>אחיסמך רבקה אימנו 43, לוד</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>אחיסמך רבקה אימנו</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>43</v>
+      </c>
+      <c r="E117" t="n">
+        <v>31.941588</v>
+      </c>
+      <c r="F117" t="n">
+        <v>34.898604</v>
+      </c>
+      <c r="G117" t="b">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>google precise match: רבקה אימנו 43, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>שבט יהודה 8, לוד</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>שבט יהודה</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>31.936617</v>
+      </c>
+      <c r="F118" t="n">
+        <v>34.8981782</v>
+      </c>
+      <c r="G118" t="b">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>google precise match: שבט יהודה 8, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>שבט זבולון 15, לוד</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>שבט זבולון</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>15</v>
+      </c>
+      <c r="E119" t="n">
+        <v>31.9407644</v>
+      </c>
+      <c r="F119" t="n">
+        <v>34.9026071</v>
+      </c>
+      <c r="G119" t="b">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>google precise match: שבט זבולון 15, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>שבט זבולון 11, לוד</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>שבט זבולון</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11</v>
+      </c>
+      <c r="E120" t="n">
+        <v>31.939077</v>
+      </c>
+      <c r="F120" t="n">
+        <v>34.901074</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>google precise match: שבט זבולון 11, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>יעקב אבינו 12, לוד</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>יעקב אבינו</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" t="n">
+        <v>31.936225</v>
+      </c>
+      <c r="F121" t="n">
+        <v>34.897088</v>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>google precise match: יעקב אבינו 12, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>צמח צדק 9, לוד</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>9</v>
+      </c>
+      <c r="E122" t="n">
+        <v>31.9419786</v>
+      </c>
+      <c r="F122" t="n">
+        <v>34.8754465</v>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>google precise match: צמח צדק 9, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>שבט אשר 30, לוד</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>שבט אשר</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>30</v>
+      </c>
+      <c r="E123" t="n">
+        <v>31.9346921</v>
+      </c>
+      <c r="F123" t="n">
+        <v>34.8993058</v>
+      </c>
+      <c r="G123" t="b">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אשר 30, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>בעל התניא 9, לוד</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>בעל התניא</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>9</v>
+      </c>
+      <c r="E124" t="n">
+        <v>31.9418437</v>
+      </c>
+      <c r="F124" t="n">
+        <v>34.8737541</v>
+      </c>
+      <c r="G124" t="b">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>google precise match: בעל התניא 9, לוד, 7132162, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>שבט יהודה 16, לוד</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>שבט יהודה</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>16</v>
+      </c>
+      <c r="E125" t="n">
+        <v>31.9375477</v>
+      </c>
+      <c r="F125" t="n">
+        <v>34.89564000000001</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>google precise match: שבט יהודה 16, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל 1, לוד</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>31.938619</v>
+      </c>
+      <c r="F126" t="n">
+        <v>34.898745</v>
+      </c>
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>google precise match: יחד שבטי ישראל 1, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל 21, לוד</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>21</v>
+      </c>
+      <c r="E127" t="n">
+        <v>31.938619</v>
+      </c>
+      <c r="F127" t="n">
+        <v>34.898745</v>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>google precise match: יחד שבטי ישראל 21, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>שבט אפרים 32, לוד</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>שבט אפרים</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>32</v>
+      </c>
+      <c r="E128" t="n">
+        <v>31.9397533</v>
+      </c>
+      <c r="F128" t="n">
+        <v>34.9003686</v>
+      </c>
+      <c r="G128" t="b">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אפרים 32, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>שבטי ישראל 25, לוד</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>25</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>google could not accurately find this address</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>שבט זבולון 20, לוד</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>שבט זבולון</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>20</v>
+      </c>
+      <c r="E130" t="n">
+        <v>31.9409507</v>
+      </c>
+      <c r="F130" t="n">
+        <v>34.902678</v>
+      </c>
+      <c r="G130" t="b">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>google precise match: שבט זבולון 20, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>שבט אפרים 3, לוד</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>שבט אפרים</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>31.939291</v>
+      </c>
+      <c r="F131" t="n">
+        <v>34.900613</v>
+      </c>
+      <c r="G131" t="b">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אפרים 3, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>שבט אשר 21, לוד</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>שבט אשר</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>21</v>
+      </c>
+      <c r="E132" t="n">
+        <v>31.9348377</v>
+      </c>
+      <c r="F132" t="n">
+        <v>34.8988273</v>
+      </c>
+      <c r="G132" t="b">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אשר 21, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>הרב עובדיה יוסף 19, לוד</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>הרב עובדיה יוסף</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>19</v>
+      </c>
+      <c r="E133" t="n">
+        <v>31.9406476</v>
+      </c>
+      <c r="F133" t="n">
+        <v>34.9018068</v>
+      </c>
+      <c r="G133" t="b">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>google precise match: הרב עובדיה יוסף 19, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>משה רבינו 5, לוד</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>משה רבינו</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>31.9373491</v>
+      </c>
+      <c r="F134" t="n">
+        <v>34.899169</v>
+      </c>
+      <c r="G134" t="b">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>google precise match: משה רבנו 5, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל 7, לוד</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>יחד שבטי ישראל</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="n">
+        <v>31.938619</v>
+      </c>
+      <c r="F135" t="n">
+        <v>34.898745</v>
+      </c>
+      <c r="G135" t="b">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>google precise match: יחד שבטי ישראל 7, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>שבט אפרים 10, לוד</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>שבט אפרים</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10</v>
+      </c>
+      <c r="E136" t="n">
+        <v>31.939803</v>
+      </c>
+      <c r="F136" t="n">
+        <v>34.900226</v>
+      </c>
+      <c r="G136" t="b">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>google precise match: שבט אפרים 10, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>צמח צדק 4, לוד</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>4</v>
+      </c>
+      <c r="E137" t="n">
+        <v>31.9431631</v>
+      </c>
+      <c r="F137" t="n">
+        <v>34.87565</v>
+      </c>
+      <c r="G137" t="b">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>google precise match: צמח צדק 4, לוד, 7132117, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>צמח צדק 9, לוד</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>צמח צדק</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>9</v>
+      </c>
+      <c r="E138" t="n">
+        <v>31.9419786</v>
+      </c>
+      <c r="F138" t="n">
+        <v>34.8754465</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>google precise match: צמח צדק 9, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>משה רבנו 17, לוד</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>משה רבנו</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>17</v>
+      </c>
+      <c r="E139" t="n">
+        <v>31.9385218</v>
+      </c>
+      <c r="F139" t="n">
+        <v>34.8970749</v>
+      </c>
+      <c r="G139" t="b">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>google precise match: משה רבנו 17, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>שבט זבולון 21, לוד</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>שבט זבולון</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>21</v>
+      </c>
+      <c r="E140" t="n">
+        <v>31.9411508</v>
+      </c>
+      <c r="F140" t="n">
+        <v>34.9025428</v>
+      </c>
+      <c r="G140" t="b">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>google precise match: שבט זבולון 21, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>יצחק אבינו 8, לוד</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>יצחק אבינו</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="n">
+        <v>31.93571</v>
+      </c>
+      <c r="F141" t="n">
+        <v>34.896836</v>
+      </c>
+      <c r="G141" t="b">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>google precise match: יעקב אבינו 8, לוד, ישראל</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>יעקב אבינו 7, לוד</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>יעקב אבינו</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>7</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="b">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>google could not accurately find this address</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>יעקב אבינו 17, לוד</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>לוד</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>יעקב אבינו</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="b">
+      <c r="D143" t="n">
+        <v>17</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="b">
         <v>0</v>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>google could not accurately find this address</t>
         </is>
